--- a/Objectif_tmc_2020_2024.xlsx
+++ b/Objectif_tmc_2020_2024.xlsx
@@ -1,33 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zanh.duo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathurin.adou\Desktop\GS2E\BIG ANALYTICS\CIE\dcpic_cie-main\dcpic_cie-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8D1F8C-1B73-45F1-AE70-CB0F0C7C086B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25596" windowHeight="10068"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -43,9 +31,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="[$-1040C]dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="[$-1040C]dd/mm/yyyy"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -134,10 +122,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -415,15 +403,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D85"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.8">
+    <row r="1" spans="1:2" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -431,7 +419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15">
+    <row r="2" spans="1:2">
       <c r="A2" s="3">
         <v>43831</v>
       </c>
@@ -439,7 +427,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15">
+    <row r="3" spans="1:2">
       <c r="A3" s="4">
         <v>43862</v>
       </c>
@@ -447,7 +435,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15">
+    <row r="4" spans="1:2">
       <c r="A4" s="3">
         <v>43891</v>
       </c>
@@ -455,7 +443,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15">
+    <row r="5" spans="1:2">
       <c r="A5" s="4">
         <v>43922</v>
       </c>
@@ -463,7 +451,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15">
+    <row r="6" spans="1:2">
       <c r="A6" s="3">
         <v>43952</v>
       </c>
@@ -471,7 +459,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15">
+    <row r="7" spans="1:2">
       <c r="A7" s="4">
         <v>43983</v>
       </c>
@@ -479,7 +467,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15">
+    <row r="8" spans="1:2">
       <c r="A8" s="3">
         <v>44013</v>
       </c>
@@ -487,7 +475,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15">
+    <row r="9" spans="1:2">
       <c r="A9" s="4">
         <v>44044</v>
       </c>
@@ -495,7 +483,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15">
+    <row r="10" spans="1:2">
       <c r="A10" s="3">
         <v>44075</v>
       </c>
@@ -503,7 +491,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15">
+    <row r="11" spans="1:2">
       <c r="A11" s="4">
         <v>44105</v>
       </c>
@@ -511,7 +499,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15">
+    <row r="12" spans="1:2">
       <c r="A12" s="3">
         <v>44136</v>
       </c>
@@ -519,7 +507,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15">
+    <row r="13" spans="1:2">
       <c r="A13" s="4">
         <v>44166</v>
       </c>
@@ -527,7 +515,7 @@
         <v>1.4166666666666601</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15">
+    <row r="14" spans="1:2">
       <c r="A14" s="3">
         <v>44197</v>
       </c>
@@ -535,7 +523,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15">
+    <row r="15" spans="1:2">
       <c r="A15" s="4">
         <v>44228</v>
       </c>
@@ -543,7 +531,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15">
+    <row r="16" spans="1:2">
       <c r="A16" s="3">
         <v>44256</v>
       </c>
@@ -551,7 +539,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15">
+    <row r="17" spans="1:2">
       <c r="A17" s="4">
         <v>44287</v>
       </c>
@@ -559,7 +547,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15">
+    <row r="18" spans="1:2">
       <c r="A18" s="3">
         <v>44317</v>
       </c>
@@ -567,7 +555,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15">
+    <row r="19" spans="1:2">
       <c r="A19" s="4">
         <v>44348</v>
       </c>
@@ -575,7 +563,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15">
+    <row r="20" spans="1:2">
       <c r="A20" s="3">
         <v>44378</v>
       </c>
@@ -583,7 +571,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15">
+    <row r="21" spans="1:2">
       <c r="A21" s="4">
         <v>44409</v>
       </c>
@@ -591,7 +579,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15">
+    <row r="22" spans="1:2">
       <c r="A22" s="3">
         <v>44440</v>
       </c>
@@ -599,7 +587,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15">
+    <row r="23" spans="1:2">
       <c r="A23" s="4">
         <v>44470</v>
       </c>
@@ -607,7 +595,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15">
+    <row r="24" spans="1:2">
       <c r="A24" s="3">
         <v>44501</v>
       </c>
@@ -615,7 +603,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15">
+    <row r="25" spans="1:2">
       <c r="A25" s="4">
         <v>44531</v>
       </c>
@@ -623,7 +611,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15">
+    <row r="26" spans="1:2">
       <c r="A26" s="3">
         <v>44562</v>
       </c>
@@ -631,7 +619,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15">
+    <row r="27" spans="1:2">
       <c r="A27" s="4">
         <v>44593</v>
       </c>
@@ -639,7 +627,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15">
+    <row r="28" spans="1:2">
       <c r="A28" s="3">
         <v>44621</v>
       </c>
@@ -647,7 +635,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15">
+    <row r="29" spans="1:2">
       <c r="A29" s="4">
         <v>44652</v>
       </c>
@@ -655,7 +643,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15">
+    <row r="30" spans="1:2">
       <c r="A30" s="3">
         <v>44682</v>
       </c>
@@ -663,7 +651,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15">
+    <row r="31" spans="1:2">
       <c r="A31" s="4">
         <v>44713</v>
       </c>
@@ -671,7 +659,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15">
+    <row r="32" spans="1:2">
       <c r="A32" s="3">
         <v>44743</v>
       </c>
@@ -679,7 +667,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15">
+    <row r="33" spans="1:2">
       <c r="A33" s="4">
         <v>44774</v>
       </c>
@@ -687,7 +675,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15">
+    <row r="34" spans="1:2">
       <c r="A34" s="3">
         <v>44805</v>
       </c>
@@ -695,7 +683,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15">
+    <row r="35" spans="1:2">
       <c r="A35" s="4">
         <v>44835</v>
       </c>
@@ -703,7 +691,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15">
+    <row r="36" spans="1:2">
       <c r="A36" s="3">
         <v>44866</v>
       </c>
@@ -711,7 +699,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15">
+    <row r="37" spans="1:2">
       <c r="A37" s="4">
         <v>44896</v>
       </c>
@@ -719,7 +707,7 @@
         <v>1.0833333333333299</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15">
+    <row r="38" spans="1:2">
       <c r="A38" s="3">
         <v>44927</v>
       </c>
@@ -727,7 +715,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15">
+    <row r="39" spans="1:2">
       <c r="A39" s="4">
         <v>44958</v>
       </c>
@@ -735,7 +723,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15">
+    <row r="40" spans="1:2">
       <c r="A40" s="3">
         <v>44986</v>
       </c>
@@ -743,7 +731,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15">
+    <row r="41" spans="1:2">
       <c r="A41" s="4">
         <v>45017</v>
       </c>
@@ -751,7 +739,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15">
+    <row r="42" spans="1:2">
       <c r="A42" s="3">
         <v>45047</v>
       </c>
@@ -759,7 +747,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15">
+    <row r="43" spans="1:2">
       <c r="A43" s="4">
         <v>45078</v>
       </c>
@@ -767,7 +755,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15">
+    <row r="44" spans="1:2">
       <c r="A44" s="3">
         <v>45108</v>
       </c>
@@ -775,7 +763,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15">
+    <row r="45" spans="1:2">
       <c r="A45" s="4">
         <v>45139</v>
       </c>
@@ -783,7 +771,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15">
+    <row r="46" spans="1:2">
       <c r="A46" s="3">
         <v>45170</v>
       </c>
@@ -791,7 +779,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15">
+    <row r="47" spans="1:2">
       <c r="A47" s="4">
         <v>45200</v>
       </c>
@@ -799,7 +787,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15">
+    <row r="48" spans="1:2">
       <c r="A48" s="3">
         <v>45231</v>
       </c>
@@ -807,7 +795,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15">
+    <row r="49" spans="1:4">
       <c r="A49" s="4">
         <v>45261</v>
       </c>
@@ -815,7 +803,7 @@
         <v>0.91666666666666596</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15">
+    <row r="50" spans="1:4">
       <c r="A50" s="3">
         <v>45292</v>
       </c>
@@ -824,7 +812,7 @@
       </c>
       <c r="D50" s="5"/>
     </row>
-    <row r="51" spans="1:4" ht="15">
+    <row r="51" spans="1:4">
       <c r="A51" s="4">
         <v>45323</v>
       </c>
@@ -832,7 +820,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15">
+    <row r="52" spans="1:4">
       <c r="A52" s="3">
         <v>45352</v>
       </c>
@@ -840,7 +828,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15">
+    <row r="53" spans="1:4">
       <c r="A53" s="4">
         <v>45383</v>
       </c>
@@ -848,7 +836,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15">
+    <row r="54" spans="1:4">
       <c r="A54" s="3">
         <v>45413</v>
       </c>
@@ -856,7 +844,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15">
+    <row r="55" spans="1:4">
       <c r="A55" s="4">
         <v>45444</v>
       </c>
@@ -864,7 +852,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15">
+    <row r="56" spans="1:4">
       <c r="A56" s="3">
         <v>45474</v>
       </c>
@@ -872,7 +860,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15">
+    <row r="57" spans="1:4">
       <c r="A57" s="4">
         <v>45505</v>
       </c>
@@ -880,7 +868,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15">
+    <row r="58" spans="1:4">
       <c r="A58" s="3">
         <v>45536</v>
       </c>
@@ -888,7 +876,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15">
+    <row r="59" spans="1:4">
       <c r="A59" s="4">
         <v>45566</v>
       </c>
@@ -896,7 +884,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15">
+    <row r="60" spans="1:4">
       <c r="A60" s="3">
         <v>45597</v>
       </c>
@@ -904,7 +892,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15">
+    <row r="61" spans="1:4">
       <c r="A61" s="4">
         <v>45627</v>
       </c>
@@ -912,7 +900,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="15">
+    <row r="62" spans="1:4">
       <c r="A62" s="3">
         <v>45658</v>
       </c>
@@ -920,7 +908,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15">
+    <row r="63" spans="1:4">
       <c r="A63" s="3">
         <v>45689</v>
       </c>
@@ -928,7 +916,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="15">
+    <row r="64" spans="1:4">
       <c r="A64" s="3">
         <v>45717</v>
       </c>
@@ -936,7 +924,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15">
+    <row r="65" spans="1:2">
       <c r="A65" s="3">
         <v>45748</v>
       </c>
@@ -944,7 +932,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15">
+    <row r="66" spans="1:2">
       <c r="A66" s="3">
         <v>45778</v>
       </c>
@@ -952,7 +940,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15">
+    <row r="67" spans="1:2">
       <c r="A67" s="3">
         <v>45809</v>
       </c>
@@ -960,7 +948,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15">
+    <row r="68" spans="1:2">
       <c r="A68" s="3">
         <v>45839</v>
       </c>
@@ -968,7 +956,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15">
+    <row r="69" spans="1:2">
       <c r="A69" s="3">
         <v>45870</v>
       </c>
@@ -976,7 +964,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15">
+    <row r="70" spans="1:2">
       <c r="A70" s="3">
         <v>45901</v>
       </c>
@@ -984,7 +972,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15">
+    <row r="71" spans="1:2">
       <c r="A71" s="3">
         <v>45931</v>
       </c>
@@ -992,7 +980,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15">
+    <row r="72" spans="1:2">
       <c r="A72" s="3">
         <v>45962</v>
       </c>
@@ -1000,11 +988,107 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15">
+    <row r="73" spans="1:2">
       <c r="A73" s="3">
         <v>45992</v>
       </c>
       <c r="B73">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46023</v>
+      </c>
+      <c r="B74">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46054</v>
+      </c>
+      <c r="B75">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46082</v>
+      </c>
+      <c r="B76">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B77">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B78">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B79">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B80">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B81">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B82">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46296</v>
+      </c>
+      <c r="B83">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46327</v>
+      </c>
+      <c r="B84">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
+        <v>46357</v>
+      </c>
+      <c r="B85">
         <v>1.75</v>
       </c>
     </row>
